--- a/results/Int All Data -0.4/Rando_1_permute.xlsx
+++ b/results/Int All Data -0.4/Rando_1_permute.xlsx
@@ -440,577 +440,577 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.744687980784984</v>
+        <v>0.7288666066705428</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7443149735542065</v>
+        <v>0.7288666066705428</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.746841821311629</v>
+        <v>0.7294697429793486</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7437547006912255</v>
+        <v>0.727976190022609</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7437547006912255</v>
+        <v>0.7264254858047697</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7550096890437985</v>
+        <v>0.7264254858047697</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7625902323160663</v>
+        <v>0.726109629835092</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.759733240773691</v>
+        <v>0.7179116624387434</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7638536561947775</v>
+        <v>0.7138055348329315</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7638536561947775</v>
+        <v>0.7147388149266902</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7603792405283215</v>
+        <v>0.7179259502540183</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7603792405283215</v>
+        <v>0.7169783823449849</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.761326808437355</v>
+        <v>0.7172085114230131</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7629060882857441</v>
+        <v>0.7141642542484342</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7622743763463884</v>
+        <v>0.7160165266206764</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7670122158915559</v>
+        <v>0.716949806714435</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.796070965101916</v>
+        <v>0.7161736925887007</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7925965494354599</v>
+        <v>0.7194195032107578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7861937031502537</v>
+        <v>0.7130880960019264</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8067386289945875</v>
+        <v>0.7159307997290268</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8049149322528951</v>
+        <v>0.7155863681287991</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8052022125920231</v>
+        <v>0.7143229442500878</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7948646924843044</v>
+        <v>0.7067837403900155</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7945631243299014</v>
+        <v>0.7092248612557885</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7767420275895809</v>
+        <v>0.7086217249469827</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7770721713745335</v>
+        <v>0.7095692928560162</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7704249081960243</v>
+        <v>0.7155134050187952</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7755643306025191</v>
+        <v>0.7093677394085378</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.770769339796252</v>
+        <v>0.7112628752266048</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.770769339796252</v>
+        <v>0.7103153073175713</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7636633424953154</v>
+        <v>0.7112628752266048</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7657600317608608</v>
+        <v>0.7086217249469827</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7660615999152638</v>
+        <v>0.7137611473534775</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.76517118326733</v>
+        <v>0.7245716893988983</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7661330389916383</v>
+        <v>0.7223178341653287</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.779427565348657</v>
+        <v>0.7223321219806036</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7788101412245763</v>
+        <v>0.7167640651158609</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7788101412245763</v>
+        <v>0.7193194885038333</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7908555315181585</v>
+        <v>0.7200512151501135</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7810497086428709</v>
+        <v>0.7352694529557489</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7798148603947095</v>
+        <v>0.7319522032573171</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7811068599039707</v>
+        <v>0.7341774828603368</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7845669877551518</v>
+        <v>0.7365614524650101</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7845669877551518</v>
+        <v>0.7365614524650101</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7877541230824799</v>
+        <v>0.7306887793786058</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8067197690784245</v>
+        <v>0.6796517506955309</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8127781837634029</v>
+        <v>0.6897448539099464</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.812763895948128</v>
+        <v>0.7032965609419137</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8136971760418865</v>
+        <v>0.7236685089693189</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8150891902580722</v>
+        <v>0.7265397883269692</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8104942288656543</v>
+        <v>0.7217891850001562</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8070198131991981</v>
+        <v>0.7239858889726261</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8060722452901645</v>
+        <v>0.7226637897991857</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8080531079998812</v>
+        <v>0.720852856839139</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8045546888037631</v>
+        <v>0.7202782961608831</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8025309626482218</v>
+        <v>0.7228337195488556</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8025309626482218</v>
+        <v>0.7234511436729363</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8028468186178996</v>
+        <v>0.7037349111145487</v>
       </c>
     </row>
     <row r="60">
@@ -1020,177 +1020,177 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8031626745875774</v>
+        <v>0.7040507670842264</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7992422885803399</v>
+        <v>0.7025857897580368</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8068799831137075</v>
+        <v>0.7068490833318728</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8076989606852665</v>
+        <v>0.7067062051791235</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8121923833371307</v>
+        <v>0.7105250524458073</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.815350943033909</v>
+        <v>0.6956752497700613</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.820433214179304</v>
+        <v>0.6902056835786139</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8210649261186598</v>
+        <v>0.6902056835786139</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8212649555325088</v>
+        <v>0.6832981916578971</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8130083128414312</v>
+        <v>0.6972973930642754</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8130511762872559</v>
+        <v>0.6964686997783294</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8149463121053229</v>
+        <v>0.6831042583785654</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8156494631210532</v>
+        <v>0.6807218128075214</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8163526141367836</v>
+        <v>0.6715732294348806</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8175445989391201</v>
+        <v>0.6725350851591891</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8176874770918695</v>
+        <v>0.673411213991848</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8168256360744857</v>
+        <v>0.6640084980115171</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8174859236443911</v>
+        <v>0.6555819255707697</v>
       </c>
     </row>
     <row r="78">
@@ -1200,787 +1200,787 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8187207718925527</v>
+        <v>0.6558834937251725</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8190223400469555</v>
+        <v>0.6579944708059928</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8165812191811824</v>
+        <v>0.655510486494395</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8165812191811824</v>
+        <v>0.663594151368544</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8169685142272349</v>
+        <v>0.6502868612298799</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.817241506751088</v>
+        <v>0.6499995808907519</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.8110514536613764</v>
+        <v>0.6503011490451548</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8137655670510026</v>
+        <v>0.6317656615410876</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.8137655670510026</v>
+        <v>0.6255296969382926</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.8165082560711785</v>
+        <v>0.6333975205496885</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8194524985388327</v>
+        <v>0.6136113729485555</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.8073739605138127</v>
+        <v>0.578893696368304</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8118260437534814</v>
+        <v>0.578893696368304</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7962159388009056</v>
+        <v>0.5872901691448724</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7967491600669661</v>
+        <v>0.588209161423356</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7982855764695304</v>
+        <v>0.5851077529876774</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7925986449817002</v>
+        <v>0.5907788726266033</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.8033979472791046</v>
+        <v>0.5905630313638501</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7964618797278381</v>
+        <v>0.5680101912128793</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7985442811781085</v>
+        <v>0.5757080850746052</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7834801612732387</v>
+        <v>0.5671799738933039</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7828913127797078</v>
+        <v>0.5430922413733981</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7857641161709874</v>
+        <v>0.5430922413733981</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.770365280380277</v>
+        <v>0.5440398092824317</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7800455609853487</v>
+        <v>0.5976480732023832</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7767997503632915</v>
+        <v>0.5959402030165197</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7795424393834675</v>
+        <v>0.5966004905864253</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7780488864267279</v>
+        <v>0.5947196425836333</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7774457501179222</v>
+        <v>0.5996447477610041</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.7732095081410066</v>
+        <v>0.5990288476705528</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7785377202133342</v>
+        <v>0.5966448780658794</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.63895148010336</v>
+        <v>0.5995115853226417</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6353612378810751</v>
+        <v>0.5795968473840344</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5542822677925211</v>
+        <v>0.6118697835186431</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5533775633293124</v>
+        <v>0.6044004947013161</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5533775633293124</v>
+        <v>0.6249056051670836</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5379832996394899</v>
+        <v>0.614914040693222</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5485096094130413</v>
+        <v>0.594445697538762</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5695336533295944</v>
+        <v>0.6048041731088838</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5692320851751915</v>
+        <v>0.5969889286576997</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5692320851751915</v>
+        <v>0.5969032017660503</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5656275551376316</v>
+        <v>0.5777314302217393</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5659291232920346</v>
+        <v>0.4993378073880578</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5719890620106424</v>
+        <v>0.5017758801865722</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5719890620106424</v>
+        <v>0.5119735702088002</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5589359044796682</v>
+        <v>0.4933426400986964</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5685860854205609</v>
+        <v>0.4892808999723388</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5270855066687902</v>
+        <v>0.485544731530046</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5346104227135876</v>
+        <v>0.485544731530046</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5468604145219068</v>
+        <v>0.4553006651644775</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5432844601148969</v>
+        <v>0.4553006651644775</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5434431501165504</v>
+        <v>0.4544403481807229</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5165020456341389</v>
+        <v>0.4544403481807229</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5224048183847225</v>
+        <v>0.4583622582215899</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5165050937013976</v>
+        <v>0.4505531099049231</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5171653812713032</v>
+        <v>0.4559558091208841</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5407892360552828</v>
+        <v>0.4531814964028996</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5634940985607788</v>
+        <v>0.4549337540682172</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5677017649071444</v>
+        <v>0.4685788081599809</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5656622269026989</v>
+        <v>0.4630505666738042</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5609243873575315</v>
+        <v>0.4571319820743164</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5647447586578446</v>
+        <v>0.4615396778345311</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5659224556449063</v>
+        <v>0.4612268699321119</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5659224556449063</v>
+        <v>0.4582111883880829</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5639543567168354</v>
+        <v>0.4571508419904794</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5639543567168354</v>
+        <v>0.5140961680460441</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5432145450721516</v>
+        <v>0.5118280249971996</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5307399488077104</v>
+        <v>0.5175119084177712</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5294193736678994</v>
+        <v>0.5104487745626595</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5348506485144101</v>
+        <v>0.5104487745626595</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5348506485144101</v>
+        <v>0.5100900551471569</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5368090317280941</v>
+        <v>0.5098900257333078</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5329631328644898</v>
+        <v>0.5110820105356445</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5361104528132518</v>
+        <v>0.5128740835795282</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5233798188990838</v>
+        <v>0.5103900992679304</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5137281139245619</v>
+        <v>0.5029411944003956</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5030461622166155</v>
+        <v>0.5029411944003956</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4944247039755179</v>
+        <v>0.5003429075665984</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4939373942225409</v>
+        <v>0.5003429075665984</v>
       </c>
     </row>
   </sheetData>
